--- a/grupos/1EM - Estadisticos 20241.xlsx
+++ b/grupos/1EM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="98">
   <si>
     <t>Materia</t>
   </si>
@@ -212,21 +212,21 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
+    <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -245,67 +245,73 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>JACINTO</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
+    <t>MAZABA</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
   </si>
   <si>
     <t>LOYO</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>NICIO</t>
   </si>
   <si>
-    <t>OCHOA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>FLORES</t>
   </si>
   <si>
     <t>BALDERAS</t>
   </si>
   <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
   </si>
   <si>
     <t>JAIMES</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
   </si>
   <si>
     <t>MATIAS</t>
   </si>
   <si>
-    <t>MAXIMILIANO</t>
-  </si>
-  <si>
-    <t>SARA ALY</t>
+    <t>MANUEL ABDUL</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
   </si>
   <si>
     <t>EVELYN</t>
   </si>
   <si>
+    <t>JESUS ALAYN</t>
+  </si>
+  <si>
     <t>DIANA KELLY</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>KRISTIAN YAEL</t>
   </si>
 </sst>
 </file>
@@ -851,28 +857,28 @@
         <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>-1</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -905,13 +911,13 @@
         <v>7</v>
       </c>
       <c r="AB4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>9</v>
       </c>
       <c r="AD4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE4">
         <v>9</v>
@@ -952,28 +958,28 @@
         <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M5">
         <v>-1</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1053,28 +1059,28 @@
         <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1101,19 +1107,19 @@
         <v>-1</v>
       </c>
       <c r="Z6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA6">
         <v>6</v>
       </c>
       <c r="AB6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC6">
         <v>6</v>
       </c>
       <c r="AD6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE6">
         <v>6</v>
@@ -1154,28 +1160,28 @@
         <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K7">
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M7">
         <v>-1</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1202,7 +1208,7 @@
         <v>-1</v>
       </c>
       <c r="Z7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA7">
         <v>7</v>
@@ -1255,28 +1261,28 @@
         <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M8">
         <v>-1</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1303,19 +1309,19 @@
         <v>-1</v>
       </c>
       <c r="Z8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA8">
         <v>6</v>
       </c>
       <c r="AB8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC8">
         <v>6</v>
       </c>
       <c r="AD8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE8">
         <v>6</v>
@@ -1356,28 +1362,28 @@
         <v>10</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
         <v>-1</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1416,7 +1422,7 @@
         <v>10</v>
       </c>
       <c r="AD9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE9">
         <v>6</v>
@@ -1457,28 +1463,28 @@
         <v>10</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>-1</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1511,7 +1517,7 @@
         <v>6</v>
       </c>
       <c r="AB10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1558,28 +1564,28 @@
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M11">
         <v>-1</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1606,13 +1612,13 @@
         <v>-1</v>
       </c>
       <c r="Z11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA11">
         <v>6</v>
       </c>
       <c r="AB11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC11">
         <v>6</v>
@@ -1659,28 +1665,28 @@
         <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>-1</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1707,25 +1713,25 @@
         <v>-1</v>
       </c>
       <c r="Z12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AA12">
         <v>7</v>
       </c>
       <c r="AB12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC12">
         <v>6</v>
       </c>
       <c r="AD12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE12">
         <v>8</v>
       </c>
       <c r="AF12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG12">
         <v>10</v>
@@ -1760,28 +1766,28 @@
         <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>-1</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1808,25 +1814,25 @@
         <v>-1</v>
       </c>
       <c r="Z13">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AA13">
         <v>7</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>6</v>
       </c>
       <c r="AD13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE13">
         <v>10</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG13">
         <v>10</v>
@@ -1861,28 +1867,28 @@
         <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
         <v>-1</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1909,7 +1915,7 @@
         <v>-1</v>
       </c>
       <c r="Z14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AA14">
         <v>6</v>
@@ -1962,28 +1968,28 @@
         <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M15">
         <v>-1</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -2010,7 +2016,7 @@
         <v>-1</v>
       </c>
       <c r="Z15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA15">
         <v>6</v>
@@ -2028,7 +2034,7 @@
         <v>8</v>
       </c>
       <c r="AF15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG15">
         <v>10</v>
@@ -2063,28 +2069,28 @@
         <v>10</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>-1</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -2117,13 +2123,13 @@
         <v>7</v>
       </c>
       <c r="AB16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC16">
         <v>10</v>
       </c>
       <c r="AD16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE16">
         <v>9</v>
@@ -2164,28 +2170,28 @@
         <v>10</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M17">
         <v>-1</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2212,7 +2218,7 @@
         <v>-1</v>
       </c>
       <c r="Z17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA17">
         <v>5</v>
@@ -2265,28 +2271,28 @@
         <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
         <v>-1</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2313,7 +2319,7 @@
         <v>-1</v>
       </c>
       <c r="Z18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA18">
         <v>7</v>
@@ -2325,7 +2331,7 @@
         <v>8</v>
       </c>
       <c r="AD18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE18">
         <v>8</v>
@@ -2366,28 +2372,28 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>-1</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2420,13 +2426,13 @@
         <v>8</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
         <v>10</v>
       </c>
       <c r="AD19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE19">
         <v>9</v>
@@ -2467,28 +2473,28 @@
         <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K20">
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>-1</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2568,28 +2574,28 @@
         <v>10</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
         <v>-1</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2616,7 +2622,7 @@
         <v>-1</v>
       </c>
       <c r="Z21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA21">
         <v>8</v>
@@ -2634,7 +2640,7 @@
         <v>6</v>
       </c>
       <c r="AF21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG21">
         <v>10</v>
@@ -2669,28 +2675,28 @@
         <v>10</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M22">
         <v>-1</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2735,7 +2741,7 @@
         <v>6</v>
       </c>
       <c r="AF22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>10</v>
@@ -2770,28 +2776,28 @@
         <v>10</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2824,13 +2830,13 @@
         <v>7</v>
       </c>
       <c r="AB23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC23">
         <v>9</v>
       </c>
       <c r="AD23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE23">
         <v>6</v>
@@ -2871,28 +2877,28 @@
         <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>-1</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2919,7 +2925,7 @@
         <v>-1</v>
       </c>
       <c r="Z24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA24">
         <v>5</v>
@@ -2931,7 +2937,7 @@
         <v>7</v>
       </c>
       <c r="AD24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE24">
         <v>5</v>
@@ -2972,28 +2978,28 @@
         <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M25">
         <v>-1</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -3020,13 +3026,13 @@
         <v>-1</v>
       </c>
       <c r="Z25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AA25">
         <v>5</v>
       </c>
       <c r="AB25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC25">
         <v>6</v>
@@ -3038,7 +3044,7 @@
         <v>7</v>
       </c>
       <c r="AF25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG25">
         <v>10</v>
@@ -3073,28 +3079,28 @@
         <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>-1</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -3121,13 +3127,13 @@
         <v>-1</v>
       </c>
       <c r="Z26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AA26">
         <v>6</v>
       </c>
       <c r="AB26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC26">
         <v>6</v>
@@ -3174,28 +3180,28 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M27">
         <v>-1</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -3240,7 +3246,7 @@
         <v>6</v>
       </c>
       <c r="AF27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG27">
         <v>10</v>
@@ -3257,7 +3263,7 @@
         <v>6</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E28">
         <v>10</v>
@@ -3275,28 +3281,28 @@
         <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K28">
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>-1</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -3323,25 +3329,25 @@
         <v>-1</v>
       </c>
       <c r="Z28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA28">
         <v>6</v>
       </c>
       <c r="AB28">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AC28">
         <v>10</v>
       </c>
       <c r="AD28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE28">
         <v>9</v>
       </c>
       <c r="AF28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG28">
         <v>10</v>
@@ -3376,28 +3382,28 @@
         <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>-1</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -3424,13 +3430,13 @@
         <v>-1</v>
       </c>
       <c r="Z29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA29">
         <v>6</v>
       </c>
       <c r="AB29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC29">
         <v>7</v>
@@ -3442,7 +3448,7 @@
         <v>7</v>
       </c>
       <c r="AF29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG29">
         <v>10</v>
@@ -3477,28 +3483,28 @@
         <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>-1</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3525,7 +3531,7 @@
         <v>-1</v>
       </c>
       <c r="Z30">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AA30">
         <v>6</v>
@@ -3543,7 +3549,7 @@
         <v>8</v>
       </c>
       <c r="AF30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG30">
         <v>10</v>
@@ -3578,28 +3584,28 @@
         <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>-1</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3632,19 +3638,19 @@
         <v>6</v>
       </c>
       <c r="AB31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC31">
         <v>10</v>
       </c>
       <c r="AD31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE31">
         <v>6</v>
       </c>
       <c r="AF31">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AG31">
         <v>10</v>
@@ -3679,28 +3685,28 @@
         <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>-1</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3733,13 +3739,13 @@
         <v>8</v>
       </c>
       <c r="AB32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>10</v>
       </c>
       <c r="AD32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE32">
         <v>7</v>
@@ -3780,28 +3786,28 @@
         <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>-1</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3840,7 +3846,7 @@
         <v>7</v>
       </c>
       <c r="AD33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AE33">
         <v>6</v>
@@ -3881,28 +3887,28 @@
         <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M34">
         <v>-1</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3929,7 +3935,7 @@
         <v>-1</v>
       </c>
       <c r="Z34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA34">
         <v>8</v>
@@ -3941,7 +3947,7 @@
         <v>8</v>
       </c>
       <c r="AD34">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE34">
         <v>10</v>
@@ -3982,28 +3988,28 @@
         <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M35">
         <v>-1</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -4030,7 +4036,7 @@
         <v>-1</v>
       </c>
       <c r="Z35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA35">
         <v>6</v>
@@ -4048,7 +4054,7 @@
         <v>7</v>
       </c>
       <c r="AF35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG35">
         <v>10</v>
@@ -4083,28 +4089,28 @@
         <v>10</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M36">
         <v>-1</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -4131,13 +4137,13 @@
         <v>-1</v>
       </c>
       <c r="Z36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA36">
         <v>7</v>
       </c>
       <c r="AB36">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC36">
         <v>6</v>
@@ -4184,28 +4190,28 @@
         <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>-1</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -4250,7 +4256,7 @@
         <v>5</v>
       </c>
       <c r="AF37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG37">
         <v>10</v>
@@ -4285,28 +4291,28 @@
         <v>10</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K38">
         <v>-1</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M38">
         <v>-1</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -4345,13 +4351,13 @@
         <v>6</v>
       </c>
       <c r="AD38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE38">
         <v>6</v>
       </c>
       <c r="AF38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG38">
         <v>10</v>
@@ -4386,28 +4392,28 @@
         <v>10</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K39">
         <v>-1</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M39">
         <v>-1</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -4434,7 +4440,7 @@
         <v>-1</v>
       </c>
       <c r="Z39">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA39">
         <v>7</v>
@@ -4452,7 +4458,7 @@
         <v>8</v>
       </c>
       <c r="AF39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG39">
         <v>10</v>
@@ -4487,28 +4493,28 @@
         <v>10</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K40">
         <v>-1</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M40">
         <v>-1</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -4535,25 +4541,25 @@
         <v>-1</v>
       </c>
       <c r="Z40">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AA40">
         <v>7</v>
       </c>
       <c r="AB40">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC40">
         <v>6</v>
       </c>
       <c r="AD40">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AE40">
         <v>6</v>
       </c>
       <c r="AF40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG40">
         <v>10</v>
@@ -4799,7 +4805,7 @@
         <v>100</v>
       </c>
       <c r="J5">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="K5">
         <v>80</v>
@@ -4811,19 +4817,19 @@
         <v>100</v>
       </c>
       <c r="N5">
+        <v>87.5</v>
+      </c>
+      <c r="O5">
+        <v>100</v>
+      </c>
+      <c r="P5">
+        <v>81.8</v>
+      </c>
+      <c r="Q5">
+        <v>100</v>
+      </c>
+      <c r="R5">
         <v>75</v>
-      </c>
-      <c r="O5">
-        <v>100</v>
-      </c>
-      <c r="P5">
-        <v>75</v>
-      </c>
-      <c r="Q5">
-        <v>100</v>
-      </c>
-      <c r="R5">
-        <v>50</v>
       </c>
       <c r="S5">
         <v>80</v>
@@ -4835,13 +4841,13 @@
         <v>100</v>
       </c>
       <c r="V5">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="W5">
         <v>100</v>
       </c>
       <c r="X5">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="Y5">
         <v>100</v>
@@ -4894,7 +4900,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4918,7 +4924,7 @@
         <v>100</v>
       </c>
       <c r="X6">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="Y6">
         <v>100</v>
@@ -5030,7 +5036,7 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K8">
         <v>93.3</v>
@@ -5048,13 +5054,13 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q8">
         <v>100</v>
       </c>
       <c r="R8">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S8">
         <v>93.3</v>
@@ -5072,7 +5078,7 @@
         <v>100</v>
       </c>
       <c r="X8">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y8">
         <v>100</v>
@@ -5261,13 +5267,13 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K11">
         <v>100</v>
       </c>
       <c r="L11">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -5279,19 +5285,19 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Q11">
         <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S11">
         <v>100</v>
       </c>
       <c r="T11">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U11">
         <v>100</v>
@@ -5303,7 +5309,7 @@
         <v>100</v>
       </c>
       <c r="X11">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Y11">
         <v>100</v>
@@ -5338,7 +5344,7 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K12">
         <v>100</v>
@@ -5362,7 +5368,7 @@
         <v>100</v>
       </c>
       <c r="R12">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S12">
         <v>100</v>
@@ -5421,19 +5427,19 @@
         <v>100</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="M13">
         <v>100</v>
       </c>
       <c r="N13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O13">
         <v>100</v>
       </c>
       <c r="P13">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="Q13">
         <v>100</v>
@@ -5445,19 +5451,19 @@
         <v>100</v>
       </c>
       <c r="T13">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="W13">
         <v>100</v>
       </c>
       <c r="X13">
-        <v>90</v>
+        <v>93.2</v>
       </c>
       <c r="Y13">
         <v>100</v>
@@ -5510,7 +5516,7 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5534,7 +5540,7 @@
         <v>100</v>
       </c>
       <c r="X14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y14">
         <v>100</v>
@@ -5569,13 +5575,13 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K15">
         <v>100</v>
       </c>
       <c r="L15">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M15">
         <v>100</v>
@@ -5593,13 +5599,13 @@
         <v>100</v>
       </c>
       <c r="R15">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S15">
         <v>100</v>
       </c>
       <c r="T15">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -5646,13 +5652,13 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K16">
         <v>100</v>
       </c>
       <c r="L16">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M16">
         <v>100</v>
@@ -5664,19 +5670,19 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S16">
         <v>100</v>
       </c>
       <c r="T16">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U16">
         <v>100</v>
@@ -5688,7 +5694,7 @@
         <v>100</v>
       </c>
       <c r="X16">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y16">
         <v>100</v>
@@ -5741,7 +5747,7 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5765,7 +5771,7 @@
         <v>100</v>
       </c>
       <c r="X17">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y17">
         <v>100</v>
@@ -5806,7 +5812,7 @@
         <v>100</v>
       </c>
       <c r="L18">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M18">
         <v>100</v>
@@ -5830,7 +5836,7 @@
         <v>100</v>
       </c>
       <c r="T18">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U18">
         <v>100</v>
@@ -5877,13 +5883,13 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K19">
         <v>100</v>
       </c>
       <c r="L19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -5895,19 +5901,19 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S19">
         <v>100</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U19">
         <v>100</v>
@@ -5919,7 +5925,7 @@
         <v>100</v>
       </c>
       <c r="X19">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="Y19">
         <v>100</v>
@@ -5954,13 +5960,13 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K20">
         <v>80</v>
       </c>
       <c r="L20">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M20">
         <v>100</v>
@@ -5972,19 +5978,19 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q20">
         <v>100</v>
       </c>
       <c r="R20">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S20">
         <v>80</v>
       </c>
       <c r="T20">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U20">
         <v>100</v>
@@ -5996,7 +6002,7 @@
         <v>100</v>
       </c>
       <c r="X20">
-        <v>75</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y20">
         <v>100</v>
@@ -6031,7 +6037,7 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K21">
         <v>100</v>
@@ -6055,7 +6061,7 @@
         <v>100</v>
       </c>
       <c r="R21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S21">
         <v>100</v>
@@ -6114,7 +6120,7 @@
         <v>100</v>
       </c>
       <c r="L22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M22">
         <v>100</v>
@@ -6126,7 +6132,7 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q22">
         <v>100</v>
@@ -6138,7 +6144,7 @@
         <v>100</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -6150,7 +6156,7 @@
         <v>100</v>
       </c>
       <c r="X22">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y22">
         <v>100</v>
@@ -6268,13 +6274,13 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="M24">
         <v>100</v>
       </c>
       <c r="N24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -6292,13 +6298,13 @@
         <v>100</v>
       </c>
       <c r="T24">
-        <v>100</v>
+        <v>97.7</v>
       </c>
       <c r="U24">
         <v>100</v>
       </c>
       <c r="V24">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="W24">
         <v>100</v>
@@ -6345,19 +6351,19 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M25">
         <v>100</v>
       </c>
       <c r="N25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O25">
         <v>100</v>
       </c>
       <c r="P25">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q25">
         <v>100</v>
@@ -6369,19 +6375,19 @@
         <v>100</v>
       </c>
       <c r="T25">
-        <v>95.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="W25">
         <v>100</v>
       </c>
       <c r="X25">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y25">
         <v>100</v>
@@ -6422,19 +6428,19 @@
         <v>100</v>
       </c>
       <c r="L26">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="M26">
         <v>100</v>
       </c>
       <c r="N26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Q26">
         <v>100</v>
@@ -6446,19 +6452,19 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>87.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="W26">
         <v>100</v>
       </c>
       <c r="X26">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -6493,13 +6499,13 @@
         <v>100</v>
       </c>
       <c r="J27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="K27">
         <v>93.3</v>
       </c>
       <c r="L27">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M27">
         <v>100</v>
@@ -6511,19 +6517,19 @@
         <v>100</v>
       </c>
       <c r="P27">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="Q27">
+        <v>100</v>
+      </c>
+      <c r="R27">
         <v>95</v>
-      </c>
-      <c r="Q27">
-        <v>100</v>
-      </c>
-      <c r="R27">
-        <v>100</v>
       </c>
       <c r="S27">
         <v>93.3</v>
       </c>
       <c r="T27">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U27">
         <v>100</v>
@@ -6535,7 +6541,7 @@
         <v>100</v>
       </c>
       <c r="X27">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y27">
         <v>100</v>
@@ -6588,7 +6594,7 @@
         <v>100</v>
       </c>
       <c r="P28">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -6612,7 +6618,7 @@
         <v>100</v>
       </c>
       <c r="X28">
-        <v>95</v>
+        <v>93.2</v>
       </c>
       <c r="Y28">
         <v>100</v>
@@ -6647,19 +6653,19 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K29">
         <v>100</v>
       </c>
       <c r="L29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="M29">
         <v>100</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -6671,19 +6677,19 @@
         <v>100</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="S29">
         <v>100</v>
       </c>
       <c r="T29">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="U29">
         <v>100</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="W29">
         <v>100</v>
@@ -6730,7 +6736,7 @@
         <v>100</v>
       </c>
       <c r="L30">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -6742,7 +6748,7 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Q30">
         <v>100</v>
@@ -6754,7 +6760,7 @@
         <v>100</v>
       </c>
       <c r="T30">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="U30">
         <v>100</v>
@@ -6766,7 +6772,7 @@
         <v>100</v>
       </c>
       <c r="X30">
-        <v>95</v>
+        <v>95.5</v>
       </c>
       <c r="Y30">
         <v>100</v>
@@ -6807,19 +6813,19 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M31">
         <v>100</v>
       </c>
       <c r="N31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
       <c r="P31">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Q31">
         <v>100</v>
@@ -6831,19 +6837,19 @@
         <v>100</v>
       </c>
       <c r="T31">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W31">
         <v>100</v>
       </c>
       <c r="X31">
-        <v>90</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y31">
         <v>100</v>
@@ -6955,49 +6961,49 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="K33">
         <v>100</v>
       </c>
       <c r="L33">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="M33">
         <v>100</v>
       </c>
       <c r="N33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O33">
         <v>100</v>
       </c>
       <c r="P33">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="S33">
         <v>100</v>
       </c>
       <c r="T33">
-        <v>95.8</v>
+        <v>97.7</v>
       </c>
       <c r="U33">
         <v>100</v>
       </c>
       <c r="V33">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W33">
         <v>100</v>
       </c>
       <c r="X33">
-        <v>75</v>
+        <v>79.5</v>
       </c>
       <c r="Y33">
         <v>100</v>
@@ -7192,19 +7198,19 @@
         <v>100</v>
       </c>
       <c r="L36">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="M36">
         <v>100</v>
       </c>
       <c r="N36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="O36">
         <v>100</v>
       </c>
       <c r="P36">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Q36">
         <v>100</v>
@@ -7216,19 +7222,19 @@
         <v>100</v>
       </c>
       <c r="T36">
-        <v>87.5</v>
+        <v>93.2</v>
       </c>
       <c r="U36">
         <v>100</v>
       </c>
       <c r="V36">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W36">
         <v>100</v>
       </c>
       <c r="X36">
-        <v>95</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y36">
         <v>100</v>
@@ -7263,49 +7269,49 @@
         <v>100</v>
       </c>
       <c r="J37">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="K37">
         <v>86.7</v>
       </c>
       <c r="L37">
-        <v>83.3</v>
+        <v>79.5</v>
       </c>
       <c r="M37">
         <v>100</v>
       </c>
       <c r="N37">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="O37">
         <v>100</v>
       </c>
       <c r="P37">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="Q37">
+        <v>100</v>
+      </c>
+      <c r="R37">
         <v>85</v>
-      </c>
-      <c r="Q37">
-        <v>100</v>
-      </c>
-      <c r="R37">
-        <v>80</v>
       </c>
       <c r="S37">
         <v>86.7</v>
       </c>
       <c r="T37">
-        <v>83.3</v>
+        <v>79.5</v>
       </c>
       <c r="U37">
         <v>100</v>
       </c>
       <c r="V37">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="W37">
         <v>100</v>
       </c>
       <c r="X37">
-        <v>85</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="Y37">
         <v>100</v>
@@ -7340,7 +7346,7 @@
         <v>100</v>
       </c>
       <c r="J38">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -7352,20 +7358,20 @@
         <v>100</v>
       </c>
       <c r="N38">
+        <v>95</v>
+      </c>
+      <c r="O38">
+        <v>100</v>
+      </c>
+      <c r="P38">
+        <v>100</v>
+      </c>
+      <c r="Q38">
+        <v>100</v>
+      </c>
+      <c r="R38">
         <v>90</v>
       </c>
-      <c r="O38">
-        <v>100</v>
-      </c>
-      <c r="P38">
-        <v>100</v>
-      </c>
-      <c r="Q38">
-        <v>100</v>
-      </c>
-      <c r="R38">
-        <v>100</v>
-      </c>
       <c r="S38">
         <v>100</v>
       </c>
@@ -7376,7 +7382,7 @@
         <v>100</v>
       </c>
       <c r="V38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="W38">
         <v>100</v>
@@ -7494,7 +7500,7 @@
         <v>100</v>
       </c>
       <c r="J40">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -7518,7 +7524,7 @@
         <v>100</v>
       </c>
       <c r="R40">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="S40">
         <v>100</v>
@@ -7628,7 +7634,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -7649,7 +7655,7 @@
         <v>21.6</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -7692,7 +7698,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -7701,19 +7707,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>83.8</v>
+        <v>86.5</v>
       </c>
       <c r="G5" s="2">
-        <v>16.2</v>
+        <v>13.5</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7724,7 +7730,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -7733,19 +7739,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F6" s="2">
-        <v>86.5</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G6" s="2">
-        <v>13.5</v>
+        <v>8.1</v>
       </c>
       <c r="H6">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7756,7 +7762,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -7765,19 +7771,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>91.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7891,7 +7897,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7923,22 +7929,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920049</v>
+        <v>24330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7946,22 +7952,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920049</v>
+        <v>24330051920040</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7969,22 +7975,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920057</v>
+        <v>24330051920049</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7992,22 +7998,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920057</v>
+        <v>24330051920049</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8015,22 +8021,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920040</v>
+        <v>24330051920373</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8038,10 +8044,10 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920366</v>
+        <v>24330051920373</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
         <v>85</v>
@@ -8050,10 +8056,10 @@
         <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -8061,10 +8067,10 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920374</v>
+        <v>24330051920038</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
         <v>86</v>
@@ -8076,7 +8082,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8084,16 +8090,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920053</v>
+        <v>24330051920038</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -8107,24 +8113,93 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>24330051920054</v>
+        <v>23330051920341</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
       </c>
       <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920366</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>24330051920364</v>
+      </c>
+      <c r="B12" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+      <c r="D12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920374</v>
+      </c>
+      <c r="B13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20241.xlsx
+++ b/grupos/1EM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -218,6 +218,9 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -227,9 +230,6 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Desc Desc Desc</t>
   </si>
   <si>
@@ -245,22 +245,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
     <t>JACINTO</t>
   </si>
   <si>
     <t>MAZABA</t>
   </si>
   <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>LOYO</t>
+    <t>MONTIEL</t>
   </si>
   <si>
     <t>MORALES</t>
@@ -269,7 +260,7 @@
     <t>NICIO</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>TZITZIHUA</t>
   </si>
   <si>
     <t>BALDERAS</t>
@@ -281,16 +272,10 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>JAIMES</t>
-  </si>
-  <si>
     <t>AVILA</t>
   </si>
   <si>
-    <t>SARA ALY</t>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>MATIAS</t>
@@ -299,19 +284,16 @@
     <t>MANUEL ABDUL</t>
   </si>
   <si>
-    <t>DIANA CAMILA</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
-  </si>
-  <si>
-    <t>EVELYN</t>
+    <t>MARIA FERNANDA</t>
   </si>
   <si>
     <t>JESUS ALAYN</t>
   </si>
   <si>
     <t>DIANA KELLY</t>
+  </si>
+  <si>
+    <t>IRVIN</t>
   </si>
 </sst>
 </file>
@@ -860,19 +842,19 @@
         <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L4">
         <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>8</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>10</v>
@@ -908,13 +890,13 @@
         <v>10</v>
       </c>
       <c r="AA4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB4">
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD4">
         <v>8</v>
@@ -961,19 +943,19 @@
         <v>5</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>5</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N5">
         <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -1015,7 +997,7 @@
         <v>5</v>
       </c>
       <c r="AC5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD5">
         <v>5</v>
@@ -1062,19 +1044,19 @@
         <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L6">
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>8</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -1110,19 +1092,19 @@
         <v>5</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB6">
         <v>8</v>
       </c>
       <c r="AC6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD6">
         <v>8</v>
       </c>
       <c r="AE6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF6">
         <v>5</v>
@@ -1163,19 +1145,19 @@
         <v>6</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>8</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>7</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1217,7 +1199,7 @@
         <v>9</v>
       </c>
       <c r="AC7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD7">
         <v>7</v>
@@ -1264,19 +1246,19 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L8">
         <v>5</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
         <v>6</v>
@@ -1312,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="AA8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB8">
         <v>6</v>
@@ -1365,19 +1347,19 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P9">
         <v>10</v>
@@ -1413,7 +1395,7 @@
         <v>9</v>
       </c>
       <c r="AA9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB9">
         <v>9</v>
@@ -1425,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="AE9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF9">
         <v>10</v>
@@ -1466,19 +1448,19 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
         <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P10">
         <v>10</v>
@@ -1514,7 +1496,7 @@
         <v>10</v>
       </c>
       <c r="AA10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB10">
         <v>10</v>
@@ -1567,19 +1549,19 @@
         <v>5</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>5</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>6</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>6</v>
@@ -1615,13 +1597,13 @@
         <v>5</v>
       </c>
       <c r="AA11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB11">
         <v>7</v>
       </c>
       <c r="AC11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD11">
         <v>7</v>
@@ -1668,19 +1650,19 @@
         <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P12">
         <v>10</v>
@@ -1716,19 +1698,19 @@
         <v>9</v>
       </c>
       <c r="AA12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB12">
         <v>9</v>
       </c>
       <c r="AC12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD12">
         <v>9</v>
       </c>
       <c r="AE12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF12">
         <v>9</v>
@@ -1769,19 +1751,19 @@
         <v>5</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L13">
         <v>8</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N13">
         <v>7</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>10</v>
@@ -1817,13 +1799,13 @@
         <v>7</v>
       </c>
       <c r="AA13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB13">
         <v>9</v>
       </c>
       <c r="AC13">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD13">
         <v>8</v>
@@ -1870,19 +1852,19 @@
         <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
         <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>8</v>
@@ -1924,13 +1906,13 @@
         <v>8</v>
       </c>
       <c r="AC14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD14">
         <v>7</v>
       </c>
       <c r="AE14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14">
         <v>9</v>
@@ -1971,19 +1953,19 @@
         <v>9</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>9</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
         <v>10</v>
@@ -2019,19 +2001,19 @@
         <v>8</v>
       </c>
       <c r="AA15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB15">
         <v>9</v>
       </c>
       <c r="AC15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD15">
         <v>8</v>
       </c>
       <c r="AE15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF15">
         <v>8</v>
@@ -2072,19 +2054,19 @@
         <v>8</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N16">
         <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>10</v>
@@ -2120,19 +2102,19 @@
         <v>9</v>
       </c>
       <c r="AA16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB16">
         <v>10</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD16">
         <v>10</v>
       </c>
       <c r="AE16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF16">
         <v>10</v>
@@ -2173,19 +2155,19 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -2227,7 +2209,7 @@
         <v>7</v>
       </c>
       <c r="AC17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD17">
         <v>6</v>
@@ -2274,19 +2256,19 @@
         <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
         <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>10</v>
@@ -2322,19 +2304,19 @@
         <v>9</v>
       </c>
       <c r="AA18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB18">
         <v>9</v>
       </c>
       <c r="AC18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD18">
         <v>9</v>
       </c>
       <c r="AE18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF18">
         <v>10</v>
@@ -2375,19 +2357,19 @@
         <v>7</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N19">
         <v>9</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
         <v>7</v>
@@ -2429,7 +2411,7 @@
         <v>8</v>
       </c>
       <c r="AC19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD19">
         <v>9</v>
@@ -2476,19 +2458,19 @@
         <v>8</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L20">
         <v>8</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2524,13 +2506,13 @@
         <v>9</v>
       </c>
       <c r="AA20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB20">
         <v>9</v>
       </c>
       <c r="AC20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD20">
         <v>8</v>
@@ -2577,19 +2559,19 @@
         <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
         <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>8</v>
@@ -2625,19 +2607,19 @@
         <v>7</v>
       </c>
       <c r="AA21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AB21">
         <v>9</v>
       </c>
       <c r="AC21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD21">
         <v>7</v>
       </c>
       <c r="AE21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF21">
         <v>8</v>
@@ -2678,19 +2660,19 @@
         <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>5</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N22">
         <v>6</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>9</v>
@@ -2732,7 +2714,7 @@
         <v>5</v>
       </c>
       <c r="AC22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD22">
         <v>6</v>
@@ -2779,19 +2761,19 @@
         <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P23">
         <v>9</v>
@@ -2827,19 +2809,19 @@
         <v>10</v>
       </c>
       <c r="AA23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB23">
         <v>9</v>
       </c>
       <c r="AC23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD23">
         <v>9</v>
       </c>
       <c r="AE23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF23">
         <v>9</v>
@@ -2880,19 +2862,19 @@
         <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>5</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
         <v>6</v>
@@ -2934,13 +2916,13 @@
         <v>5</v>
       </c>
       <c r="AC24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AD24">
         <v>6</v>
       </c>
       <c r="AE24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF24">
         <v>6</v>
@@ -2981,19 +2963,19 @@
         <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
         <v>7</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>6</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P25">
         <v>8</v>
@@ -3041,7 +3023,7 @@
         <v>6</v>
       </c>
       <c r="AE25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF25">
         <v>7</v>
@@ -3082,19 +3064,19 @@
         <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P26">
         <v>7</v>
@@ -3130,19 +3112,19 @@
         <v>5</v>
       </c>
       <c r="AA26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AB26">
         <v>5</v>
       </c>
       <c r="AC26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD26">
         <v>7</v>
       </c>
       <c r="AE26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF26">
         <v>7</v>
@@ -3183,19 +3165,19 @@
         <v>8</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>7</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>6</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>8</v>
@@ -3231,13 +3213,13 @@
         <v>5</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>8</v>
       </c>
       <c r="AC27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AD27">
         <v>6</v>
@@ -3284,19 +3266,19 @@
         <v>7</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N28">
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
         <v>9</v>
@@ -3338,13 +3320,13 @@
         <v>8</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD28">
         <v>8</v>
       </c>
       <c r="AE28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF28">
         <v>9</v>
@@ -3385,19 +3367,19 @@
         <v>5</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L29">
         <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>6</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P29">
         <v>7</v>
@@ -3439,13 +3421,13 @@
         <v>7</v>
       </c>
       <c r="AC29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD29">
         <v>6</v>
       </c>
       <c r="AE29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF29">
         <v>6</v>
@@ -3486,19 +3468,19 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
         <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>7</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
         <v>10</v>
@@ -3534,19 +3516,19 @@
         <v>9</v>
       </c>
       <c r="AA30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>9</v>
       </c>
       <c r="AC30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD30">
         <v>7</v>
       </c>
       <c r="AE30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF30">
         <v>9</v>
@@ -3587,19 +3569,19 @@
         <v>7</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>8</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>7</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>8</v>
@@ -3641,13 +3623,13 @@
         <v>7</v>
       </c>
       <c r="AC31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AD31">
         <v>6</v>
       </c>
       <c r="AE31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF31">
         <v>7</v>
@@ -3688,19 +3670,19 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>10</v>
@@ -3789,19 +3771,19 @@
         <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L33">
         <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N33">
         <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>6</v>
@@ -3843,13 +3825,13 @@
         <v>5</v>
       </c>
       <c r="AC33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD33">
         <v>7</v>
       </c>
       <c r="AE33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF33">
         <v>5</v>
@@ -3890,19 +3872,19 @@
         <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
         <v>9</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N34">
         <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
         <v>10</v>
@@ -3938,19 +3920,19 @@
         <v>9</v>
       </c>
       <c r="AA34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB34">
         <v>9</v>
       </c>
       <c r="AC34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AD34">
         <v>8</v>
       </c>
       <c r="AE34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF34">
         <v>10</v>
@@ -3991,19 +3973,19 @@
         <v>10</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L35">
         <v>9</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>7</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P35">
         <v>10</v>
@@ -4039,13 +4021,13 @@
         <v>10</v>
       </c>
       <c r="AA35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB35">
         <v>9</v>
       </c>
       <c r="AC35">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD35">
         <v>8</v>
@@ -4092,19 +4074,19 @@
         <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>7</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
         <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>6</v>
@@ -4146,7 +4128,7 @@
         <v>8</v>
       </c>
       <c r="AC36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD36">
         <v>7</v>
@@ -4193,19 +4175,19 @@
         <v>5</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L37">
         <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P37">
         <v>5</v>
@@ -4247,7 +4229,7 @@
         <v>5</v>
       </c>
       <c r="AC37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD37">
         <v>5</v>
@@ -4294,19 +4276,19 @@
         <v>7</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L38">
         <v>6</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N38">
         <v>8</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -4342,13 +4324,13 @@
         <v>5</v>
       </c>
       <c r="AA38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AB38">
         <v>5</v>
       </c>
       <c r="AC38">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AD38">
         <v>6</v>
@@ -4395,19 +4377,19 @@
         <v>10</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
         <v>9</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N39">
         <v>7</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P39">
         <v>10</v>
@@ -4449,7 +4431,7 @@
         <v>9</v>
       </c>
       <c r="AC39">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AD39">
         <v>7</v>
@@ -4496,19 +4478,19 @@
         <v>10</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L40">
         <v>8</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>10</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P40">
         <v>10</v>
@@ -4550,7 +4532,7 @@
         <v>9</v>
       </c>
       <c r="AC40">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AD40">
         <v>9</v>
@@ -5039,7 +5021,7 @@
         <v>85</v>
       </c>
       <c r="K8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -5063,7 +5045,7 @@
         <v>85</v>
       </c>
       <c r="S8">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T8">
         <v>100</v>
@@ -5270,7 +5252,7 @@
         <v>90</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L11">
         <v>88.59999999999999</v>
@@ -5294,7 +5276,7 @@
         <v>90</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T11">
         <v>88.59999999999999</v>
@@ -5578,7 +5560,7 @@
         <v>95</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L15">
         <v>97.7</v>
@@ -5602,7 +5584,7 @@
         <v>95</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T15">
         <v>97.7</v>
@@ -5963,7 +5945,7 @@
         <v>85</v>
       </c>
       <c r="K20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="L20">
         <v>97.7</v>
@@ -5987,7 +5969,7 @@
         <v>85</v>
       </c>
       <c r="S20">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="T20">
         <v>97.7</v>
@@ -6040,7 +6022,7 @@
         <v>95</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -6064,7 +6046,7 @@
         <v>95</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -6502,7 +6484,7 @@
         <v>95</v>
       </c>
       <c r="K27">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L27">
         <v>97.7</v>
@@ -6526,7 +6508,7 @@
         <v>95</v>
       </c>
       <c r="S27">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="T27">
         <v>97.7</v>
@@ -7195,7 +7177,7 @@
         <v>90</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L36">
         <v>93.2</v>
@@ -7219,7 +7201,7 @@
         <v>90</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="T36">
         <v>93.2</v>
@@ -7272,7 +7254,7 @@
         <v>85</v>
       </c>
       <c r="K37">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="L37">
         <v>79.5</v>
@@ -7296,7 +7278,7 @@
         <v>85</v>
       </c>
       <c r="S37">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="T37">
         <v>79.5</v>
@@ -7611,19 +7593,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="2">
-        <v>75.7</v>
+        <v>73</v>
       </c>
       <c r="G2" s="2">
-        <v>24.3</v>
+        <v>27</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -7698,7 +7680,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -7707,19 +7689,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>86.5</v>
+        <v>83.8</v>
       </c>
       <c r="G5" s="2">
-        <v>13.5</v>
+        <v>16.2</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -7730,7 +7712,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -7739,19 +7721,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>91.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="G6" s="2">
-        <v>8.1</v>
+        <v>13.5</v>
       </c>
       <c r="H6">
-        <v>7.1</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -7762,7 +7744,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -7771,19 +7753,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2">
-        <v>94.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>5.4</v>
+        <v>8.1</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7794,7 +7776,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -7803,19 +7785,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F8" s="2">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="H8">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7897,7 +7879,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7929,22 +7911,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920040</v>
+        <v>24330051920049</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7952,22 +7934,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920040</v>
+        <v>24330051920049</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7975,16 +7957,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920049</v>
+        <v>24330051920373</v>
       </c>
       <c r="B4" t="s">
         <v>76</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7998,22 +7980,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920049</v>
+        <v>24330051920373</v>
       </c>
       <c r="B5" t="s">
         <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -8021,16 +8003,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920373</v>
+        <v>24330051920052</v>
       </c>
       <c r="B6" t="s">
         <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -8044,16 +8026,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920373</v>
+        <v>24330051920052</v>
       </c>
       <c r="B7" t="s">
         <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -8067,22 +8049,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920038</v>
+        <v>24330051920364</v>
       </c>
       <c r="B8" t="s">
         <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -8090,22 +8072,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920038</v>
+        <v>24330051920374</v>
       </c>
       <c r="B9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" t="s">
         <v>78</v>
       </c>
-      <c r="C9" t="s">
-        <v>86</v>
-      </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -8113,93 +8095,24 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920341</v>
+        <v>24330051920318</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920366</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920364</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920374</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E13" t="s">
-        <v>5</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20241.xlsx
+++ b/grupos/1EM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="103">
   <si>
     <t>Materia</t>
   </si>
@@ -245,6 +245,18 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>VILLARREAL</t>
+  </si>
+  <si>
     <t>JACINTO</t>
   </si>
   <si>
@@ -263,19 +275,40 @@
     <t>TZITZIHUA</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>DE URIARTE</t>
+  </si>
+  <si>
     <t>BALDERAS</t>
   </si>
   <si>
     <t>QUINTERO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>AVILA</t>
   </si>
   <si>
     <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
   </si>
   <si>
     <t>MATIAS</t>
@@ -7062,7 +7095,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7094,22 +7127,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920049</v>
+        <v>24330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7117,22 +7150,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920049</v>
+        <v>24330051920040</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7140,22 +7173,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920373</v>
+        <v>24330051920040</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7163,22 +7196,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920373</v>
+        <v>24330051920040</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7186,22 +7219,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920052</v>
+        <v>24330051920038</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7209,22 +7242,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920052</v>
+        <v>24330051920038</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7232,22 +7265,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920364</v>
+        <v>24330051920038</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -7255,22 +7288,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920374</v>
+        <v>24330051920038</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7278,24 +7311,346 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
+        <v>23330051920341</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" t="s">
+        <v>5</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>23330051920341</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
+        <v>87</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>23330051920341</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>24330051920060</v>
+      </c>
+      <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" t="s">
+        <v>96</v>
+      </c>
+      <c r="E13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>24330051920060</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>24330051920060</v>
+      </c>
+      <c r="B15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>24330051920049</v>
+      </c>
+      <c r="B16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
+        <v>24330051920049</v>
+      </c>
+      <c r="B17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" t="s">
+        <v>97</v>
+      </c>
+      <c r="E17" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>24330051920373</v>
+      </c>
+      <c r="B18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
+        <v>6</v>
+      </c>
+      <c r="F18" t="s">
+        <v>63</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>24330051920373</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F19" t="s">
+        <v>65</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>24330051920052</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>24330051920052</v>
+      </c>
+      <c r="B21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" t="s">
+        <v>99</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>24330051920364</v>
+      </c>
+      <c r="B22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>24330051920374</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>82</v>
+      </c>
+      <c r="D23" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
         <v>24330051920318</v>
       </c>
-      <c r="B10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="B24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C24" t="s">
+        <v>92</v>
+      </c>
+      <c r="D24" t="s">
+        <v>102</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
         <v>66</v>
       </c>
-      <c r="G10">
+      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20241.xlsx
+++ b/grupos/1EM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="104">
   <si>
     <t>Materia</t>
   </si>
@@ -212,24 +212,24 @@
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -245,88 +245,91 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>JACINTO</t>
+  </si>
+  <si>
     <t>MOTA</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
+    <t>MAZABA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>TZITZIHUA</t>
   </si>
   <si>
     <t>VILLARREAL</t>
   </si>
   <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>MAZABA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>NICIO</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
+    <t>MORA</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>ROSAS</t>
+    <t>QUINTERO</t>
+  </si>
+  <si>
+    <t>AVILA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
   </si>
   <si>
     <t>DE URIARTE</t>
   </si>
   <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>ANGEL GAEL</t>
   </si>
   <si>
     <t>SARA ALY</t>
   </si>
   <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>MATIAS</t>
+  </si>
+  <si>
     <t>DIANA CAMILA</t>
   </si>
   <si>
-    <t>DAMARIZ</t>
+    <t>MANUEL ABDUL</t>
+  </si>
+  <si>
+    <t>JESUS ALAYN</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>IRVIN</t>
   </si>
   <si>
     <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>MANUEL ABDUL</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>JESUS ALAYN</t>
-  </si>
-  <si>
-    <t>DIANA KELLY</t>
-  </si>
-  <si>
-    <t>IRVIN</t>
   </si>
 </sst>
 </file>
@@ -874,13 +877,13 @@
         <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -921,7 +924,7 @@
         <v>14</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -963,13 +966,13 @@
         <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -984,7 +987,7 @@
         <v>-1</v>
       </c>
       <c r="W5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X5">
         <v>5</v>
@@ -1052,13 +1055,13 @@
         <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1073,7 +1076,7 @@
         <v>-1</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>5</v>
@@ -1141,13 +1144,13 @@
         <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1162,7 +1165,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1230,13 +1233,13 @@
         <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1257,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Z8">
         <v>6</v>
@@ -1319,13 +1322,13 @@
         <v>10</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1408,13 +1411,13 @@
         <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1497,13 +1500,13 @@
         <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1518,7 +1521,7 @@
         <v>-1</v>
       </c>
       <c r="W11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X11">
         <v>5</v>
@@ -1586,13 +1589,13 @@
         <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1675,13 +1678,13 @@
         <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1764,13 +1767,13 @@
         <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1785,7 +1788,7 @@
         <v>-1</v>
       </c>
       <c r="W14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1853,13 +1856,13 @@
         <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1942,13 +1945,13 @@
         <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2031,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q17">
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2058,7 +2061,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z17">
         <v>7</v>
@@ -2120,13 +2123,13 @@
         <v>10</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2209,13 +2212,13 @@
         <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2230,13 +2233,13 @@
         <v>-1</v>
       </c>
       <c r="W19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z19">
         <v>9</v>
@@ -2298,13 +2301,13 @@
         <v>7</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2319,7 +2322,7 @@
         <v>-1</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>6</v>
@@ -2387,13 +2390,13 @@
         <v>8</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2476,13 +2479,13 @@
         <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2503,7 +2506,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z22">
         <v>7</v>
@@ -2565,13 +2568,13 @@
         <v>9</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2654,13 +2657,13 @@
         <v>6</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q24">
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2675,13 +2678,13 @@
         <v>-1</v>
       </c>
       <c r="W24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>5</v>
       </c>
       <c r="Y24">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z24">
         <v>8</v>
@@ -2743,13 +2746,13 @@
         <v>8</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2770,7 +2773,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z25">
         <v>6</v>
@@ -2832,13 +2835,13 @@
         <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q26">
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2853,13 +2856,13 @@
         <v>-1</v>
       </c>
       <c r="W26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X26">
         <v>5</v>
       </c>
       <c r="Y26">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z26">
         <v>5</v>
@@ -2879,7 +2882,7 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C27">
         <v>6</v>
@@ -2921,13 +2924,13 @@
         <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
         <v>-1</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2942,13 +2945,13 @@
         <v>-1</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>7</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z27">
         <v>7</v>
@@ -3010,13 +3013,13 @@
         <v>9</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q28">
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -3031,7 +3034,7 @@
         <v>-1</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>6</v>
@@ -3099,13 +3102,13 @@
         <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q29">
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3188,13 +3191,13 @@
         <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3277,13 +3280,13 @@
         <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q31">
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3298,7 +3301,7 @@
         <v>-1</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>6</v>
@@ -3366,13 +3369,13 @@
         <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3393,7 +3396,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Z32">
         <v>10</v>
@@ -3413,7 +3416,7 @@
         <v>42</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33">
         <v>5</v>
@@ -3455,13 +3458,13 @@
         <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q33">
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3482,7 +3485,7 @@
         <v>5</v>
       </c>
       <c r="Y33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z33">
         <v>6</v>
@@ -3544,13 +3547,13 @@
         <v>10</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3633,13 +3636,13 @@
         <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3654,7 +3657,7 @@
         <v>-1</v>
       </c>
       <c r="W35">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3722,13 +3725,13 @@
         <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3743,13 +3746,13 @@
         <v>-1</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>7</v>
       </c>
       <c r="Y36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z36">
         <v>5</v>
@@ -3769,7 +3772,7 @@
         <v>46</v>
       </c>
       <c r="B37">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C37">
         <v>5</v>
@@ -3811,13 +3814,13 @@
         <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q37">
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3858,7 +3861,7 @@
         <v>47</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C38">
         <v>5</v>
@@ -3900,13 +3903,13 @@
         <v>8</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q38">
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3921,13 +3924,13 @@
         <v>-1</v>
       </c>
       <c r="W38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X38">
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Z38">
         <v>5</v>
@@ -3989,13 +3992,13 @@
         <v>10</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q39">
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -4078,13 +4081,13 @@
         <v>10</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q40">
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -4357,13 +4360,13 @@
         <v>81.8</v>
       </c>
       <c r="P5">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q5">
         <v>80</v>
       </c>
       <c r="R5">
-        <v>75</v>
+        <v>82.8</v>
       </c>
       <c r="S5">
         <v>100</v>
@@ -4425,7 +4428,7 @@
         <v>93.2</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -4561,7 +4564,7 @@
         <v>97.7</v>
       </c>
       <c r="P8">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="Q8">
         <v>96.7</v>
@@ -4765,13 +4768,13 @@
         <v>95.5</v>
       </c>
       <c r="P11">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q11">
         <v>96.7</v>
       </c>
       <c r="R11">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4833,7 +4836,7 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q12">
         <v>100</v>
@@ -4907,7 +4910,7 @@
         <v>100</v>
       </c>
       <c r="R13">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S13">
         <v>100</v>
@@ -5037,13 +5040,13 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q15">
         <v>96.7</v>
       </c>
       <c r="R15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -5105,13 +5108,13 @@
         <v>97.7</v>
       </c>
       <c r="P16">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q16">
         <v>100</v>
       </c>
       <c r="R16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S16">
         <v>100</v>
@@ -5173,7 +5176,7 @@
         <v>97.7</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q17">
         <v>100</v>
@@ -5247,7 +5250,7 @@
         <v>100</v>
       </c>
       <c r="R18">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -5309,13 +5312,13 @@
         <v>97.7</v>
       </c>
       <c r="P19">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q19">
         <v>100</v>
       </c>
       <c r="R19">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S19">
         <v>100</v>
@@ -5377,13 +5380,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P20">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q20">
         <v>90</v>
       </c>
       <c r="R20">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S20">
         <v>100</v>
@@ -5445,7 +5448,7 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="Q21">
         <v>96.7</v>
@@ -5513,13 +5516,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P22">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q22">
         <v>100</v>
       </c>
       <c r="R22">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S22">
         <v>100</v>
@@ -5655,7 +5658,7 @@
         <v>100</v>
       </c>
       <c r="R24">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S24">
         <v>100</v>
@@ -5717,13 +5720,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q25">
         <v>100</v>
       </c>
       <c r="R25">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S25">
         <v>100</v>
@@ -5785,13 +5788,13 @@
         <v>93.2</v>
       </c>
       <c r="P26">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q26">
         <v>100</v>
       </c>
       <c r="R26">
-        <v>88.59999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="S26">
         <v>100</v>
@@ -5853,13 +5856,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P27">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q27">
         <v>96.7</v>
       </c>
       <c r="R27">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S27">
         <v>100</v>
@@ -5921,7 +5924,7 @@
         <v>93.2</v>
       </c>
       <c r="P28">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q28">
         <v>100</v>
@@ -5989,13 +5992,13 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q29">
         <v>100</v>
       </c>
       <c r="R29">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="S29">
         <v>100</v>
@@ -6063,7 +6066,7 @@
         <v>100</v>
       </c>
       <c r="R30">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -6125,13 +6128,13 @@
         <v>88.59999999999999</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q31">
         <v>100</v>
       </c>
       <c r="R31">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -6261,13 +6264,13 @@
         <v>79.5</v>
       </c>
       <c r="P33">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q33">
         <v>100</v>
       </c>
       <c r="R33">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S33">
         <v>100</v>
@@ -6397,7 +6400,7 @@
         <v>100</v>
       </c>
       <c r="P35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q35">
         <v>100</v>
@@ -6465,13 +6468,13 @@
         <v>90.90000000000001</v>
       </c>
       <c r="P36">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Q36">
         <v>93.3</v>
       </c>
       <c r="R36">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
       <c r="S36">
         <v>100</v>
@@ -6533,13 +6536,13 @@
         <v>84.09999999999999</v>
       </c>
       <c r="P37">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Q37">
         <v>83.3</v>
       </c>
       <c r="R37">
-        <v>79.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -6601,7 +6604,7 @@
         <v>100</v>
       </c>
       <c r="P38">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q38">
         <v>100</v>
@@ -6737,7 +6740,7 @@
         <v>100</v>
       </c>
       <c r="P40">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Q40">
         <v>100</v>
@@ -6844,7 +6847,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6853,19 +6856,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" s="2">
-        <v>78.40000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="G3" s="2">
-        <v>21.6</v>
+        <v>16.2</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6876,7 +6879,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6885,16 +6888,16 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>81.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="G4" s="2">
-        <v>18.9</v>
+        <v>13.5</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -6908,7 +6911,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -6917,19 +6920,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>83.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>16.2</v>
+        <v>8.1</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6940,7 +6943,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -6949,19 +6952,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>86.5</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6972,7 +6975,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -6981,19 +6984,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>91.90000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G7" s="2">
-        <v>8.1</v>
+        <v>5.4</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7004,7 +7007,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -7025,7 +7028,7 @@
         <v>5.4</v>
       </c>
       <c r="H8">
-        <v>7.4</v>
+        <v>7.7</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7095,7 +7098,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7127,7 +7130,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920040</v>
+        <v>24330051920375</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
@@ -7136,13 +7139,13 @@
         <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7150,7 +7153,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920040</v>
+        <v>24330051920375</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
@@ -7159,7 +7162,7 @@
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -7173,7 +7176,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920040</v>
+        <v>24330051920375</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
@@ -7182,10 +7185,10 @@
         <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -7196,7 +7199,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920040</v>
+        <v>24330051920375</v>
       </c>
       <c r="B5" t="s">
         <v>75</v>
@@ -7205,13 +7208,13 @@
         <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
         <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7219,7 +7222,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920038</v>
+        <v>24330051920040</v>
       </c>
       <c r="B6" t="s">
         <v>76</v>
@@ -7228,13 +7231,13 @@
         <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7242,7 +7245,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920038</v>
+        <v>24330051920040</v>
       </c>
       <c r="B7" t="s">
         <v>76</v>
@@ -7251,13 +7254,13 @@
         <v>86</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7265,7 +7268,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>24330051920038</v>
+        <v>24330051920040</v>
       </c>
       <c r="B8" t="s">
         <v>76</v>
@@ -7274,10 +7277,10 @@
         <v>86</v>
       </c>
       <c r="D8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F8" t="s">
         <v>65</v>
@@ -7288,22 +7291,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>24330051920038</v>
+        <v>23330051920341</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -7320,10 +7323,10 @@
         <v>87</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
         <v>64</v>
@@ -7334,16 +7337,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920341</v>
+        <v>24330051920049</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -7357,22 +7360,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920341</v>
+        <v>24330051920049</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -7380,22 +7383,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>24330051920060</v>
+        <v>24330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7403,22 +7406,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>24330051920060</v>
+        <v>24330051920038</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E14" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -7426,22 +7429,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>24330051920060</v>
+        <v>24330051920373</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7449,16 +7452,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>24330051920049</v>
+        <v>24330051920364</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7472,22 +7475,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>24330051920049</v>
+        <v>24330051920052</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C17" t="s">
         <v>89</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E17" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -7495,22 +7498,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>24330051920373</v>
+        <v>24330051920318</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D18" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -7518,139 +7521,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>24330051920373</v>
+        <v>24330051920060</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>24330051920052</v>
-      </c>
-      <c r="B20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C20" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>24330051920052</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>65</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>24330051920364</v>
-      </c>
-      <c r="B22" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" t="s">
-        <v>100</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>63</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>24330051920374</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>64</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>24330051920318</v>
-      </c>
-      <c r="B24" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" t="s">
-        <v>92</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EM - Estadisticos 20241.xlsx
+++ b/grupos/1EM - Estadisticos 20241.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="84">
   <si>
     <t>Materia</t>
   </si>
@@ -209,27 +209,27 @@
     <t>Recursos socioemocionales I</t>
   </si>
   <si>
+    <t>Ochoa Martínez Mayeli</t>
+  </si>
+  <si>
+    <t>Camacho Juárez Sergio Eduardo</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
-    <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Camacho Juárez Sergio Eduardo</t>
-  </si>
-  <si>
     <t>Faltante Faltante Faltante</t>
   </si>
   <si>
@@ -245,91 +245,31 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>VALDIVIA</t>
+  </si>
+  <si>
+    <t>ALVAREZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>JACINTO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>MAZABA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>TZITZIHUA</t>
-  </si>
-  <si>
-    <t>VILLARREAL</t>
+    <t>TENORIO</t>
+  </si>
+  <si>
+    <t>CONCHE</t>
   </si>
   <si>
     <t>MORA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>QUINTERO</t>
-  </si>
-  <si>
-    <t>AVILA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE URIARTE</t>
+    <t>IKER YHAIR</t>
+  </si>
+  <si>
+    <t>VANESSA GUADALUPE</t>
   </si>
   <si>
     <t>ANGEL GAEL</t>
-  </si>
-  <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
-  </si>
-  <si>
-    <t>MATIAS</t>
-  </si>
-  <si>
-    <t>DIANA CAMILA</t>
-  </si>
-  <si>
-    <t>MANUEL ABDUL</t>
-  </si>
-  <si>
-    <t>JESUS ALAYN</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>IRVIN</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
   </si>
 </sst>
 </file>
@@ -880,22 +820,22 @@
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -907,7 +847,7 @@
         <v>10</v>
       </c>
       <c r="Z4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA4">
         <v>8</v>
@@ -969,43 +909,43 @@
         <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R5">
         <v>5</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>6</v>
       </c>
       <c r="X5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y5">
         <v>5</v>
       </c>
       <c r="Z5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:29">
@@ -1058,34 +998,34 @@
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
         <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>6</v>
       </c>
       <c r="X6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y6">
         <v>8</v>
       </c>
       <c r="Z6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA6">
         <v>8</v>
@@ -1094,7 +1034,7 @@
         <v>7</v>
       </c>
       <c r="AC6">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:29">
@@ -1147,28 +1087,28 @@
         <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>9</v>
@@ -1180,7 +1120,7 @@
         <v>7</v>
       </c>
       <c r="AB7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC7">
         <v>8</v>
@@ -1236,22 +1176,22 @@
         <v>8</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1266,13 +1206,13 @@
         <v>6</v>
       </c>
       <c r="AA8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC8">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:29">
@@ -1325,22 +1265,22 @@
         <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1358,7 +1298,7 @@
         <v>8</v>
       </c>
       <c r="AB9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC9">
         <v>10</v>
@@ -1414,28 +1354,28 @@
         <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R10">
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W10">
         <v>10</v>
       </c>
       <c r="X10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1447,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="AB10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC10">
         <v>10</v>
@@ -1503,34 +1443,34 @@
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>6</v>
       </c>
       <c r="X11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y11">
         <v>7</v>
       </c>
       <c r="Z11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA11">
         <v>7</v>
@@ -1592,22 +1532,22 @@
         <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R12">
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1681,40 +1621,40 @@
         <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R13">
         <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
         <v>7</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>9</v>
       </c>
       <c r="Z13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AA13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC13">
         <v>9</v>
@@ -1770,22 +1710,22 @@
         <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1800,7 +1740,7 @@
         <v>8</v>
       </c>
       <c r="AA14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB14">
         <v>8</v>
@@ -1859,22 +1799,22 @@
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>10</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1948,22 +1888,22 @@
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>9</v>
@@ -1975,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="Z16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA16">
         <v>10</v>
       </c>
       <c r="AB16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC16">
         <v>10</v>
@@ -2037,28 +1977,28 @@
         <v>7</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>8</v>
@@ -2073,7 +2013,7 @@
         <v>6</v>
       </c>
       <c r="AC17">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:29">
@@ -2126,22 +2066,22 @@
         <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2215,22 +2155,22 @@
         <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2248,10 +2188,10 @@
         <v>9</v>
       </c>
       <c r="AB19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:29">
@@ -2304,22 +2244,22 @@
         <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W20">
         <v>8</v>
@@ -2331,13 +2271,13 @@
         <v>9</v>
       </c>
       <c r="Z20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA20">
         <v>8</v>
       </c>
       <c r="AB20">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC20">
         <v>7</v>
@@ -2393,37 +2333,37 @@
         <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
         <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
         <v>7</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
       </c>
       <c r="Z21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB21">
         <v>7</v>
@@ -2482,28 +2422,28 @@
         <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>10</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>6</v>
       </c>
       <c r="X22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2512,7 +2452,7 @@
         <v>7</v>
       </c>
       <c r="AA22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB22">
         <v>6</v>
@@ -2571,22 +2511,22 @@
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>10</v>
@@ -2598,7 +2538,7 @@
         <v>9</v>
       </c>
       <c r="Z23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA23">
         <v>9</v>
@@ -2660,28 +2600,28 @@
         <v>10</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
         <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>9</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2690,13 +2630,13 @@
         <v>8</v>
       </c>
       <c r="AA24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB24">
         <v>7</v>
       </c>
       <c r="AC24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:29">
@@ -2749,28 +2689,28 @@
         <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R25">
         <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>7</v>
       </c>
       <c r="X25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y25">
         <v>8</v>
@@ -2779,7 +2719,7 @@
         <v>6</v>
       </c>
       <c r="AA25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB25">
         <v>8</v>
@@ -2838,37 +2778,37 @@
         <v>7</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
       </c>
       <c r="Z26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB26">
         <v>8</v>
@@ -2927,37 +2867,37 @@
         <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R27">
         <v>7</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>8</v>
       </c>
       <c r="X27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y27">
         <v>7</v>
       </c>
       <c r="Z27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB27">
         <v>6</v>
@@ -3016,22 +2956,22 @@
         <v>8</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
         <v>8</v>
@@ -3105,22 +3045,22 @@
         <v>6</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R29">
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -3194,22 +3134,22 @@
         <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -3221,10 +3161,10 @@
         <v>9</v>
       </c>
       <c r="Z30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB30">
         <v>9</v>
@@ -3283,22 +3223,22 @@
         <v>5</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R31">
         <v>6</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3310,16 +3250,16 @@
         <v>7</v>
       </c>
       <c r="Z31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AA31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC31">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:29">
@@ -3372,22 +3312,22 @@
         <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
         <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3405,7 +3345,7 @@
         <v>9</v>
       </c>
       <c r="AB32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC32">
         <v>10</v>
@@ -3461,28 +3401,28 @@
         <v>5</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>5</v>
       </c>
       <c r="X33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3494,10 +3434,10 @@
         <v>7</v>
       </c>
       <c r="AB33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:29">
@@ -3550,22 +3490,22 @@
         <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
         <v>10</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W34">
         <v>9</v>
@@ -3639,28 +3579,28 @@
         <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>9</v>
       </c>
       <c r="X35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y35">
         <v>9</v>
@@ -3672,7 +3612,7 @@
         <v>8</v>
       </c>
       <c r="AB35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AC35">
         <v>9</v>
@@ -3728,22 +3668,22 @@
         <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
         <v>5</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3755,7 +3695,7 @@
         <v>7</v>
       </c>
       <c r="Z36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA36">
         <v>7</v>
@@ -3817,22 +3757,22 @@
         <v>5</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
         <v>5</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W37">
         <v>5</v>
@@ -3847,13 +3787,13 @@
         <v>6</v>
       </c>
       <c r="AA37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AB37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC37">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:29">
@@ -3906,40 +3846,40 @@
         <v>7</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R38">
         <v>10</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>6</v>
       </c>
       <c r="X38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y38">
         <v>7</v>
       </c>
       <c r="Z38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AA38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AB38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC38">
         <v>7</v>
@@ -3995,22 +3935,22 @@
         <v>9</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R39">
         <v>10</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W39">
         <v>8</v>
@@ -4022,13 +3962,13 @@
         <v>9</v>
       </c>
       <c r="Z39">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA39">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AB39">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC39">
         <v>9</v>
@@ -4084,28 +4024,28 @@
         <v>10</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R40">
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W40">
         <v>10</v>
       </c>
       <c r="X40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y40">
         <v>9</v>
@@ -4117,7 +4057,7 @@
         <v>9</v>
       </c>
       <c r="AB40">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AC40">
         <v>9</v>
@@ -4363,22 +4303,22 @@
         <v>84.40000000000001</v>
       </c>
       <c r="Q5">
-        <v>80</v>
+        <v>83.3</v>
       </c>
       <c r="R5">
         <v>82.8</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T5">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="U5">
         <v>100</v>
       </c>
       <c r="V5">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:22">
@@ -4446,7 +4386,7 @@
         <v>100</v>
       </c>
       <c r="V6">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -4514,7 +4454,7 @@
         <v>100</v>
       </c>
       <c r="V7">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -4567,7 +4507,7 @@
         <v>87.5</v>
       </c>
       <c r="Q8">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -4582,7 +4522,7 @@
         <v>100</v>
       </c>
       <c r="V8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -4771,7 +4711,7 @@
         <v>87.5</v>
       </c>
       <c r="Q11">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R11">
         <v>92.2</v>
@@ -4786,7 +4726,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -4913,16 +4853,16 @@
         <v>96.90000000000001</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T13">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U13">
         <v>100</v>
       </c>
       <c r="V13">
-        <v>93.2</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="14" spans="1:22">
@@ -4981,7 +4921,7 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T14">
         <v>100</v>
@@ -4990,7 +4930,7 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -5043,7 +4983,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q15">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R15">
         <v>98.40000000000001</v>
@@ -5058,7 +4998,7 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:22">
@@ -5126,7 +5066,7 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>97.7</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -5194,7 +5134,7 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="18" spans="1:22">
@@ -5262,7 +5202,7 @@
         <v>100</v>
       </c>
       <c r="V18">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -5330,7 +5270,7 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>97.7</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -5383,13 +5323,13 @@
         <v>90.59999999999999</v>
       </c>
       <c r="Q20">
-        <v>90</v>
+        <v>91.7</v>
       </c>
       <c r="R20">
         <v>98.40000000000001</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -5398,7 +5338,7 @@
         <v>100</v>
       </c>
       <c r="V20">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="21" spans="1:22">
@@ -5451,13 +5391,13 @@
         <v>93.8</v>
       </c>
       <c r="Q21">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R21">
         <v>100</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T21">
         <v>100</v>
@@ -5466,7 +5406,7 @@
         <v>100</v>
       </c>
       <c r="V21">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="22" spans="1:22">
@@ -5519,7 +5459,7 @@
         <v>93.8</v>
       </c>
       <c r="Q22">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R22">
         <v>95.3</v>
@@ -5534,7 +5474,7 @@
         <v>100</v>
       </c>
       <c r="V22">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="23" spans="1:22">
@@ -5661,10 +5601,10 @@
         <v>98.40000000000001</v>
       </c>
       <c r="S24">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T24">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="U24">
         <v>100</v>
@@ -5723,22 +5663,22 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R25">
         <v>92.2</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T25">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U25">
         <v>100</v>
       </c>
       <c r="V25">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="26" spans="1:22">
@@ -5800,13 +5740,13 @@
         <v>100</v>
       </c>
       <c r="T26">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="U26">
         <v>100</v>
       </c>
       <c r="V26">
-        <v>93.2</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -5859,7 +5799,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q27">
-        <v>96.7</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R27">
         <v>98.40000000000001</v>
@@ -5874,7 +5814,7 @@
         <v>100</v>
       </c>
       <c r="V27">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:22">
@@ -5942,7 +5882,7 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>93.2</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -6004,13 +5944,13 @@
         <v>100</v>
       </c>
       <c r="T29">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U29">
         <v>100</v>
       </c>
       <c r="V29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -6063,13 +6003,13 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R30">
         <v>95.3</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T30">
         <v>100</v>
@@ -6078,7 +6018,7 @@
         <v>100</v>
       </c>
       <c r="V30">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -6131,22 +6071,22 @@
         <v>96.90000000000001</v>
       </c>
       <c r="Q31">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="R31">
         <v>98.40000000000001</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T31">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>88.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:22">
@@ -6205,7 +6145,7 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T32">
         <v>100</v>
@@ -6276,13 +6216,13 @@
         <v>100</v>
       </c>
       <c r="T33">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U33">
         <v>100</v>
       </c>
       <c r="V33">
-        <v>79.5</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -6341,7 +6281,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -6471,22 +6411,22 @@
         <v>90.59999999999999</v>
       </c>
       <c r="Q36">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="R36">
         <v>95.3</v>
       </c>
       <c r="S36">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="T36">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U36">
         <v>100</v>
       </c>
       <c r="V36">
-        <v>90.90000000000001</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="37" spans="1:22">
@@ -6545,16 +6485,16 @@
         <v>85.90000000000001</v>
       </c>
       <c r="S37">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="T37">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="U37">
         <v>100</v>
       </c>
       <c r="V37">
-        <v>84.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="38" spans="1:22">
@@ -6616,13 +6556,13 @@
         <v>100</v>
       </c>
       <c r="T38">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="U38">
         <v>100</v>
       </c>
       <c r="V38">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:22">
@@ -6815,7 +6755,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
@@ -6824,19 +6764,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>73</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>27</v>
+        <v>5.4</v>
       </c>
       <c r="H2">
-        <v>6.6</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6847,7 +6787,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>64</v>
@@ -6856,16 +6796,16 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
-        <v>83.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>16.2</v>
+        <v>5.4</v>
       </c>
       <c r="H3">
         <v>7.7</v>
@@ -6879,7 +6819,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>65</v>
@@ -6888,19 +6828,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>86.5</v>
+        <v>97.3</v>
       </c>
       <c r="G4" s="2">
-        <v>13.5</v>
+        <v>2.7</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6911,7 +6851,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
@@ -6920,19 +6860,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>91.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6943,7 +6883,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
@@ -6952,19 +6892,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="2">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6975,7 +6915,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>68</v>
@@ -6984,19 +6924,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="2">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G7" s="2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -7007,7 +6947,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
         <v>69</v>
@@ -7016,19 +6956,19 @@
         <v>37</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>94.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -7098,7 +7038,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7130,22 +7070,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920375</v>
+        <v>24330051920341</v>
       </c>
       <c r="B2" t="s">
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7153,22 +7093,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920375</v>
+        <v>24330051920341</v>
       </c>
       <c r="B3" t="s">
         <v>75</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7176,22 +7116,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920375</v>
+        <v>24330051920341</v>
       </c>
       <c r="B4" t="s">
         <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -7199,22 +7139,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920375</v>
+        <v>24330051920215</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7222,323 +7162,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920040</v>
+        <v>24330051920375</v>
       </c>
       <c r="B6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920040</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>64</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920040</v>
-      </c>
-      <c r="B8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" t="s">
-        <v>86</v>
-      </c>
-      <c r="D8" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920341</v>
-      </c>
-      <c r="B9" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>96</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>63</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920341</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>96</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>64</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920049</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>63</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>24330051920049</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D12" t="s">
-        <v>97</v>
-      </c>
-      <c r="E12" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" t="s">
-        <v>65</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>24330051920038</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>24330051920038</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" t="s">
-        <v>98</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>64</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>24330051920373</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" t="s">
-        <v>99</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>63</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>24330051920364</v>
-      </c>
-      <c r="B16" t="s">
-        <v>81</v>
-      </c>
-      <c r="C16" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" t="s">
-        <v>100</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>63</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>24330051920052</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>101</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>63</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>24330051920318</v>
-      </c>
-      <c r="B18" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
-      <c r="D18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>24330051920060</v>
-      </c>
-      <c r="B19" t="s">
-        <v>84</v>
-      </c>
-      <c r="C19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" t="s">
-        <v>103</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>64</v>
-      </c>
-      <c r="G19">
         <v>5</v>
       </c>
     </row>
